--- a/sample_data/수집일지_샘플.xlsx
+++ b/sample_data/수집일지_샘플.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>O-0001</t>
+          <t>P-0001</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O-0002</t>
+          <t>P-0002</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X-0001</t>
+          <t>F-0001</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O-0003</t>
+          <t>P-0003</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>X-0002</t>
+          <t>F-0002</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O-0004</t>
+          <t>P-0004</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>O-0005</t>
+          <t>P-0005</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O-0006</t>
+          <t>P-0006</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X-0003</t>
+          <t>F-0003</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O-0007</t>
+          <t>P-0007</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">

--- a/sample_data/수집일지_샘플.xlsx
+++ b/sample_data/수집일지_샘플.xlsx
@@ -421,7 +421,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>bCODE</t>
+          <t>내부코드</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>bCODE</t>
+          <t>내부코드</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
